--- a/artfynd/A 69012-2021 artfynd.xlsx
+++ b/artfynd/A 69012-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 69012-2021 artfynd.xlsx
+++ b/artfynd/A 69012-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3245,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112794214</v>
+        <v>112795633</v>
       </c>
       <c r="B27" t="n">
-        <v>96129</v>
+        <v>96123</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3261,23 +3261,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3285,13 +3281,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>872753</v>
+        <v>872624</v>
       </c>
       <c r="R27" t="n">
-        <v>7315121</v>
+        <v>7315387</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3335,22 +3331,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112794211</v>
+        <v>112794214</v>
       </c>
       <c r="B28" t="n">
-        <v>89714</v>
+        <v>96129</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3363,21 +3359,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3215</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3387,10 +3383,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>872615</v>
+        <v>872753</v>
       </c>
       <c r="R28" t="n">
-        <v>7315389</v>
+        <v>7315121</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3449,10 +3445,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112794207</v>
+        <v>112794211</v>
       </c>
       <c r="B29" t="n">
-        <v>56769</v>
+        <v>89714</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3461,25 +3457,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3489,10 +3485,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>872750</v>
+        <v>872615</v>
       </c>
       <c r="R29" t="n">
-        <v>7315274</v>
+        <v>7315389</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3525,11 +3521,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-10-17</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3556,10 +3547,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112794231</v>
+        <v>112794207</v>
       </c>
       <c r="B30" t="n">
-        <v>78018</v>
+        <v>56769</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3572,21 +3563,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3596,10 +3587,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>872687</v>
+        <v>872750</v>
       </c>
       <c r="R30" t="n">
-        <v>7315269</v>
+        <v>7315274</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3632,6 +3623,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3658,10 +3654,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112794225</v>
+        <v>112794231</v>
       </c>
       <c r="B31" t="n">
-        <v>97165</v>
+        <v>78018</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3670,25 +3666,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3694,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>872622</v>
+        <v>872687</v>
       </c>
       <c r="R31" t="n">
-        <v>7315384</v>
+        <v>7315269</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3734,11 +3730,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-10-17</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ca 30 ex</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3765,10 +3756,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112794213</v>
+        <v>112794225</v>
       </c>
       <c r="B32" t="n">
-        <v>96129</v>
+        <v>97165</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3777,25 +3768,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3805,10 +3796,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>872648</v>
+        <v>872622</v>
       </c>
       <c r="R32" t="n">
-        <v>7315341</v>
+        <v>7315384</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3841,6 +3832,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ca 30 ex</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3867,10 +3863,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112795623</v>
+        <v>112794213</v>
       </c>
       <c r="B33" t="n">
-        <v>89714</v>
+        <v>96129</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3883,21 +3879,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3215</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3907,13 +3903,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>872591</v>
+        <v>872648</v>
       </c>
       <c r="R33" t="n">
-        <v>7315392</v>
+        <v>7315341</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3957,22 +3953,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112795657</v>
+        <v>112794240</v>
       </c>
       <c r="B34" t="n">
-        <v>78018</v>
+        <v>96123</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3981,27 +3977,23 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>221944</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4009,13 +4001,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>872597</v>
+        <v>872613</v>
       </c>
       <c r="R34" t="n">
-        <v>7315240</v>
+        <v>7315392</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4059,22 +4051,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112794222</v>
+        <v>112795623</v>
       </c>
       <c r="B35" t="n">
-        <v>97165</v>
+        <v>89714</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4083,25 +4075,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4111,13 +4103,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>872615</v>
+        <v>872591</v>
       </c>
       <c r="R35" t="n">
-        <v>7315393</v>
+        <v>7315392</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4147,11 +4139,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-10-17</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ca 50 ex</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4166,22 +4153,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112795662</v>
+        <v>112795657</v>
       </c>
       <c r="B36" t="n">
-        <v>81755</v>
+        <v>78018</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4194,21 +4181,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4218,10 +4205,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>872624</v>
+        <v>872597</v>
       </c>
       <c r="R36" t="n">
-        <v>7315336</v>
+        <v>7315240</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4280,10 +4267,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112795601</v>
+        <v>112794222</v>
       </c>
       <c r="B37" t="n">
-        <v>86755</v>
+        <v>97165</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4292,25 +4279,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4320,13 +4307,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>872619</v>
+        <v>872615</v>
       </c>
       <c r="R37" t="n">
-        <v>7315391</v>
+        <v>7315393</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4356,6 +4343,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ca 50 ex</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4370,22 +4362,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112794233</v>
+        <v>112795662</v>
       </c>
       <c r="B38" t="n">
-        <v>78018</v>
+        <v>81755</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4398,21 +4390,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4422,13 +4414,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>872714</v>
+        <v>872624</v>
       </c>
       <c r="R38" t="n">
-        <v>7315300</v>
+        <v>7315336</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4472,22 +4464,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112794223</v>
+        <v>112795601</v>
       </c>
       <c r="B39" t="n">
-        <v>97165</v>
+        <v>86755</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4496,25 +4488,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4524,13 +4516,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>872609</v>
+        <v>872619</v>
       </c>
       <c r="R39" t="n">
-        <v>7315386</v>
+        <v>7315391</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4560,11 +4552,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-10-17</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ca 50 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4579,22 +4566,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112795647</v>
+        <v>112794233</v>
       </c>
       <c r="B40" t="n">
-        <v>89956</v>
+        <v>78018</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4607,21 +4594,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4631,13 +4618,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>872637</v>
+        <v>872714</v>
       </c>
       <c r="R40" t="n">
-        <v>7315289</v>
+        <v>7315300</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4681,22 +4668,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112795605</v>
+        <v>112794223</v>
       </c>
       <c r="B41" t="n">
-        <v>56898</v>
+        <v>97165</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4705,25 +4692,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4733,13 +4720,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>872634</v>
+        <v>872609</v>
       </c>
       <c r="R41" t="n">
-        <v>7315119</v>
+        <v>7315386</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4769,6 +4756,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ca 50 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4783,22 +4775,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112794215</v>
+        <v>112795647</v>
       </c>
       <c r="B42" t="n">
-        <v>96129</v>
+        <v>89956</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4807,25 +4799,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4835,13 +4827,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>872746</v>
+        <v>872637</v>
       </c>
       <c r="R42" t="n">
-        <v>7315165</v>
+        <v>7315289</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4885,22 +4877,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112795644</v>
+        <v>112795605</v>
       </c>
       <c r="B43" t="n">
-        <v>97298</v>
+        <v>56898</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4909,50 +4901,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lillön, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>872621</v>
+        <v>872634</v>
       </c>
       <c r="R43" t="n">
-        <v>7315385</v>
+        <v>7315119</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4993,7 +4973,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5012,10 +4991,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112795645</v>
+        <v>112794215</v>
       </c>
       <c r="B44" t="n">
-        <v>97298</v>
+        <v>96129</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5024,53 +5003,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lillön, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>872607</v>
+        <v>872746</v>
       </c>
       <c r="R44" t="n">
-        <v>7315387</v>
+        <v>7315165</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5108,26 +5075,25 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112795643</v>
+        <v>112795644</v>
       </c>
       <c r="B45" t="n">
         <v>97298</v>
@@ -5162,7 +5128,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5179,10 +5145,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>872599</v>
+        <v>872621</v>
       </c>
       <c r="R45" t="n">
-        <v>7315395</v>
+        <v>7315385</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5239,6 +5205,236 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>112795645</v>
+      </c>
+      <c r="B46" t="n">
+        <v>97298</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lillön, Nb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>872607</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7315387</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>112795643</v>
+      </c>
+      <c r="B47" t="n">
+        <v>97298</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lillön, Nb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>872599</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7315395</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 69012-2021 artfynd.xlsx
+++ b/artfynd/A 69012-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112795663</v>
+        <v>112794200</v>
       </c>
       <c r="B2" t="n">
-        <v>81755</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>872635</v>
+        <v>872724</v>
       </c>
       <c r="R2" t="n">
-        <v>7315321</v>
+        <v>7315118</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,49 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112795624</v>
+        <v>112795604</v>
       </c>
       <c r="B3" t="n">
-        <v>89714</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>872597</v>
+        <v>872636</v>
       </c>
       <c r="R3" t="n">
-        <v>7315391</v>
+        <v>7315129</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112795602</v>
+        <v>112794235</v>
       </c>
       <c r="B4" t="n">
-        <v>86755</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4412</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>872611</v>
+        <v>872697</v>
       </c>
       <c r="R4" t="n">
-        <v>7315388</v>
+        <v>7315239</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112794227</v>
+        <v>112795661</v>
       </c>
       <c r="B5" t="n">
-        <v>89956</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>872715</v>
+        <v>872604</v>
       </c>
       <c r="R5" t="n">
-        <v>7315251</v>
+        <v>7315409</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1057,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-10-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På grangren</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112794228</v>
+        <v>112795662</v>
       </c>
       <c r="B6" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>872658</v>
+        <v>872624</v>
       </c>
       <c r="R6" t="n">
-        <v>7315375</v>
+        <v>7315336</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,49 +1148,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112794209</v>
+        <v>112795663</v>
       </c>
       <c r="B7" t="n">
-        <v>89714</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3215</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>872616</v>
+        <v>872635</v>
       </c>
       <c r="R7" t="n">
-        <v>7315382</v>
+        <v>7315321</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,27 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112795625</v>
+        <v>112794209</v>
       </c>
       <c r="B8" t="n">
-        <v>89714</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>872605</v>
+        <v>872616</v>
       </c>
       <c r="R8" t="n">
-        <v>7315397</v>
+        <v>7315381</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1382,49 +1342,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112795640</v>
+        <v>112794210</v>
       </c>
       <c r="B9" t="n">
-        <v>56879</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103035</v>
+        <v>3215</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,13 +1389,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>872650</v>
+        <v>872589</v>
       </c>
       <c r="R9" t="n">
-        <v>7315102</v>
+        <v>7315390</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1484,49 +1439,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112795656</v>
+        <v>112794211</v>
       </c>
       <c r="B10" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>3215</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,13 +1486,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>872624</v>
+        <v>872615</v>
       </c>
       <c r="R10" t="n">
-        <v>7315336</v>
+        <v>7315388</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1586,49 +1536,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112794226</v>
+        <v>112795623</v>
       </c>
       <c r="B11" t="n">
-        <v>97165</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,13 +1583,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>872612</v>
+        <v>872591</v>
       </c>
       <c r="R11" t="n">
-        <v>7315391</v>
+        <v>7315392</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1674,11 +1619,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-10-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ca 10 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,49 +1633,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112794200</v>
+        <v>112795624</v>
       </c>
       <c r="B12" t="n">
-        <v>89938</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,13 +1680,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>872725</v>
+        <v>872597</v>
       </c>
       <c r="R12" t="n">
-        <v>7315118</v>
+        <v>7315391</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1795,49 +1730,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112794232</v>
+        <v>112795625</v>
       </c>
       <c r="B13" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>3215</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,13 +1777,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>872743</v>
+        <v>872605</v>
       </c>
       <c r="R13" t="n">
-        <v>7315237</v>
+        <v>7315397</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1897,27 +1827,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112795648</v>
+        <v>112795601</v>
       </c>
       <c r="B14" t="n">
-        <v>89956</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1925,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>4412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>872632</v>
+        <v>872618</v>
       </c>
       <c r="R14" t="n">
-        <v>7315200</v>
+        <v>7315391</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112795604</v>
+        <v>112795602</v>
       </c>
       <c r="B15" t="n">
-        <v>89938</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2027,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>4412</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>872637</v>
+        <v>872611</v>
       </c>
       <c r="R15" t="n">
-        <v>7315129</v>
+        <v>7315387</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,37 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112794212</v>
+        <v>112794228</v>
       </c>
       <c r="B16" t="n">
-        <v>96129</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>872610</v>
+        <v>872658</v>
       </c>
       <c r="R16" t="n">
-        <v>7315392</v>
+        <v>7315375</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2215,37 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112794235</v>
+        <v>112794230</v>
       </c>
       <c r="B17" t="n">
-        <v>81755</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>872697</v>
+        <v>872640</v>
       </c>
       <c r="R17" t="n">
-        <v>7315240</v>
+        <v>7315403</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2317,37 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112794206</v>
+        <v>112794231</v>
       </c>
       <c r="B18" t="n">
-        <v>56769</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>872601</v>
+        <v>872687</v>
       </c>
       <c r="R18" t="n">
-        <v>7315444</v>
+        <v>7315269</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2393,11 +2298,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-10-17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2424,19 +2324,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112795658</v>
+        <v>112794232</v>
       </c>
       <c r="B19" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2464,13 +2359,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>872680</v>
+        <v>872743</v>
       </c>
       <c r="R19" t="n">
-        <v>7315354</v>
+        <v>7315237</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2514,31 +2409,26 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112795659</v>
+        <v>112794233</v>
       </c>
       <c r="B20" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2566,13 +2456,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>872667</v>
+        <v>872714</v>
       </c>
       <c r="R20" t="n">
-        <v>7315361</v>
+        <v>7315300</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2616,12 +2506,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2631,16 +2521,11 @@
         <v>112794234</v>
       </c>
       <c r="B21" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2730,15 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112794224</v>
+        <v>112795656</v>
       </c>
       <c r="B22" t="n">
-        <v>97165</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2746,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2770,13 +2650,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>872617</v>
+        <v>872624</v>
       </c>
       <c r="R22" t="n">
-        <v>7315395</v>
+        <v>7315337</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2806,11 +2686,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-10-17</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ca 40 ex</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2825,27 +2700,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112795641</v>
+        <v>112795657</v>
       </c>
       <c r="B23" t="n">
-        <v>97165</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2880,7 +2750,7 @@
         <v>872597</v>
       </c>
       <c r="R23" t="n">
-        <v>7315391</v>
+        <v>7315240</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,37 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112794210</v>
+        <v>112795658</v>
       </c>
       <c r="B24" t="n">
-        <v>89714</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3215</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2979,13 +2844,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>872589</v>
+        <v>872679</v>
       </c>
       <c r="R24" t="n">
-        <v>7315390</v>
+        <v>7315354</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3029,49 +2894,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112795661</v>
+        <v>112795659</v>
       </c>
       <c r="B25" t="n">
-        <v>81755</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3081,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>872604</v>
+        <v>872666</v>
       </c>
       <c r="R25" t="n">
-        <v>7315409</v>
+        <v>7315361</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,37 +3003,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112795646</v>
+        <v>112795660</v>
       </c>
       <c r="B26" t="n">
-        <v>89956</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3183,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>872637</v>
+        <v>872687</v>
       </c>
       <c r="R26" t="n">
-        <v>7315297</v>
+        <v>7315377</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,15 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112795633</v>
+        <v>112795665</v>
       </c>
       <c r="B27" t="n">
-        <v>96123</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3261,19 +3111,23 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221944</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3281,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>872624</v>
+        <v>872674</v>
       </c>
       <c r="R27" t="n">
-        <v>7315387</v>
+        <v>7315377</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3343,15 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112794214</v>
+        <v>112794206</v>
       </c>
       <c r="B28" t="n">
-        <v>96129</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3359,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3383,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>872753</v>
+        <v>872602</v>
       </c>
       <c r="R28" t="n">
-        <v>7315121</v>
+        <v>7315444</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3419,6 +3268,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3445,15 +3299,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112794211</v>
+        <v>112794207</v>
       </c>
       <c r="B29" t="n">
-        <v>89714</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3461,21 +3310,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3485,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>872615</v>
+        <v>872749</v>
       </c>
       <c r="R29" t="n">
-        <v>7315389</v>
+        <v>7315274</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3521,6 +3370,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3547,19 +3401,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112794207</v>
+        <v>112794208</v>
       </c>
       <c r="B30" t="n">
-        <v>56769</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3587,10 +3436,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>872750</v>
+        <v>872764</v>
       </c>
       <c r="R30" t="n">
-        <v>7315274</v>
+        <v>7315234</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3654,37 +3503,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112794231</v>
+        <v>112794218</v>
       </c>
       <c r="B31" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3694,10 +3538,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>872687</v>
+        <v>872735</v>
       </c>
       <c r="R31" t="n">
-        <v>7315269</v>
+        <v>7315199</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3756,37 +3600,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112794225</v>
+        <v>112794201</v>
       </c>
       <c r="B32" t="n">
-        <v>97165</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3796,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>872622</v>
+        <v>872764</v>
       </c>
       <c r="R32" t="n">
-        <v>7315384</v>
+        <v>7315234</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3832,11 +3671,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-10-17</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ca 30 ex</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3863,37 +3697,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112794213</v>
+        <v>112795605</v>
       </c>
       <c r="B33" t="n">
-        <v>96129</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3903,13 +3732,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>872648</v>
+        <v>872634</v>
       </c>
       <c r="R33" t="n">
-        <v>7315341</v>
+        <v>7315119</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3953,27 +3782,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112794240</v>
+        <v>112795640</v>
       </c>
       <c r="B34" t="n">
-        <v>96123</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58085</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3981,19 +3805,23 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221944</v>
+        <v>205976</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4001,13 +3829,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>872613</v>
+        <v>872649</v>
       </c>
       <c r="R34" t="n">
-        <v>7315392</v>
+        <v>7315102</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4051,49 +3879,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112795623</v>
+        <v>112794222</v>
       </c>
       <c r="B35" t="n">
-        <v>89714</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4103,13 +3926,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>872591</v>
+        <v>872615</v>
       </c>
       <c r="R35" t="n">
-        <v>7315392</v>
+        <v>7315393</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4139,6 +3962,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ca 50 ex</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4153,49 +3981,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112795657</v>
+        <v>112794223</v>
       </c>
       <c r="B36" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4205,13 +4028,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>872597</v>
+        <v>872608</v>
       </c>
       <c r="R36" t="n">
-        <v>7315240</v>
+        <v>7315386</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4241,6 +4064,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ca 50 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4255,27 +4083,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112794222</v>
+        <v>112794224</v>
       </c>
       <c r="B37" t="n">
-        <v>97165</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4307,10 +4130,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>872615</v>
+        <v>872617</v>
       </c>
       <c r="R37" t="n">
-        <v>7315393</v>
+        <v>7315396</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4347,7 +4170,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ca 50 ex</t>
+          <t>Ca 40 ex</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4374,37 +4197,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112795662</v>
+        <v>112794225</v>
       </c>
       <c r="B38" t="n">
-        <v>81755</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4414,13 +4232,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>872624</v>
+        <v>872622</v>
       </c>
       <c r="R38" t="n">
-        <v>7315336</v>
+        <v>7315383</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4450,6 +4268,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ca 30 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4464,49 +4287,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112795601</v>
+        <v>112794226</v>
       </c>
       <c r="B39" t="n">
-        <v>86755</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4516,13 +4334,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>872619</v>
+        <v>872612</v>
       </c>
       <c r="R39" t="n">
-        <v>7315391</v>
+        <v>7315390</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4552,6 +4370,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ca 10 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4566,49 +4389,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112794233</v>
+        <v>112795641</v>
       </c>
       <c r="B40" t="n">
-        <v>78018</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4618,13 +4436,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>872714</v>
+        <v>872597</v>
       </c>
       <c r="R40" t="n">
-        <v>7315300</v>
+        <v>7315391</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4668,27 +4486,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112794223</v>
+        <v>112795643</v>
       </c>
       <c r="B41" t="n">
-        <v>97165</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4713,20 +4526,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lillön, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>872609</v>
+        <v>872599</v>
       </c>
       <c r="R41" t="n">
-        <v>7315386</v>
+        <v>7315395</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4758,79 +4583,82 @@
           <t>2023-10-17</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ca 50 ex</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112795647</v>
+        <v>112795644</v>
       </c>
       <c r="B42" t="n">
-        <v>89956</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lillön, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>872637</v>
+        <v>872620</v>
       </c>
       <c r="R42" t="n">
-        <v>7315289</v>
+        <v>7315385</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4871,6 +4699,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4889,50 +4718,57 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112795605</v>
+        <v>112795645</v>
       </c>
       <c r="B43" t="n">
-        <v>56898</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lillön, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>872634</v>
+        <v>872606</v>
       </c>
       <c r="R43" t="n">
-        <v>7315119</v>
+        <v>7315386</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4973,6 +4809,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4991,15 +4828,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112794215</v>
+        <v>112794240</v>
       </c>
       <c r="B44" t="n">
-        <v>96129</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97977</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5007,23 +4839,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5031,10 +4859,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>872746</v>
+        <v>872613</v>
       </c>
       <c r="R44" t="n">
-        <v>7315165</v>
+        <v>7315392</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5093,62 +4921,41 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112795644</v>
+        <v>112795633</v>
       </c>
       <c r="B45" t="n">
-        <v>97298</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97977</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>221944</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lillön, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>872621</v>
+        <v>872624</v>
       </c>
       <c r="R45" t="n">
-        <v>7315385</v>
+        <v>7315387</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5189,7 +4996,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5208,65 +5014,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112795645</v>
+        <v>112794212</v>
       </c>
       <c r="B46" t="n">
-        <v>97298</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lillön, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>872607</v>
+        <v>872610</v>
       </c>
       <c r="R46" t="n">
-        <v>7315387</v>
+        <v>7315392</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5304,84 +5093,66 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112795643</v>
+        <v>112794213</v>
       </c>
       <c r="B47" t="n">
-        <v>97298</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lillön, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>872599</v>
+        <v>872647</v>
       </c>
       <c r="R47" t="n">
-        <v>7315395</v>
+        <v>7315341</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5419,22 +5190,215 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>112794214</v>
+      </c>
+      <c r="B48" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lillön, Nb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>872752</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7315121</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>112794215</v>
+      </c>
+      <c r="B49" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lillön, Nb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>872747</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7315165</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 69012-2021 artfynd.xlsx
+++ b/artfynd/A 69012-2021 artfynd.xlsx
@@ -1805,7 +1805,7 @@
         <v>112795625</v>
       </c>
       <c r="B13" t="n">
-        <v>91680</v>
+        <v>91835</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Sara Karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 69012-2021 artfynd.xlsx
+++ b/artfynd/A 69012-2021 artfynd.xlsx
@@ -1805,7 +1805,7 @@
         <v>112795625</v>
       </c>
       <c r="B13" t="n">
-        <v>91835</v>
+        <v>91836</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 69012-2021 artfynd.xlsx
+++ b/artfynd/A 69012-2021 artfynd.xlsx
@@ -1805,7 +1805,7 @@
         <v>112795625</v>
       </c>
       <c r="B13" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 69012-2021 artfynd.xlsx
+++ b/artfynd/A 69012-2021 artfynd.xlsx
@@ -1805,7 +1805,7 @@
         <v>112795625</v>
       </c>
       <c r="B13" t="n">
-        <v>91837</v>
+        <v>91843</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Sara Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 69012-2021 artfynd.xlsx
+++ b/artfynd/A 69012-2021 artfynd.xlsx
@@ -1805,7 +1805,7 @@
         <v>112795625</v>
       </c>
       <c r="B13" t="n">
-        <v>91843</v>
+        <v>91844</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 69012-2021 artfynd.xlsx
+++ b/artfynd/A 69012-2021 artfynd.xlsx
@@ -1805,7 +1805,7 @@
         <v>112795625</v>
       </c>
       <c r="B13" t="n">
-        <v>91844</v>
+        <v>91850</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 69012-2021 artfynd.xlsx
+++ b/artfynd/A 69012-2021 artfynd.xlsx
@@ -1805,7 +1805,7 @@
         <v>112795625</v>
       </c>
       <c r="B13" t="n">
-        <v>91850</v>
+        <v>91857</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
